--- a/logs/Consolidado_05_03_2026.xlsx
+++ b/logs/Consolidado_05_03_2026.xlsx
@@ -269,8 +269,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Marca_Oral_Care" displayName="Marca_Oral_Care" ref="A1:H6" headerRowCount="1">
-  <autoFilter ref="A1:H6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Marca_Oral_Care" displayName="Marca_Oral_Care" ref="A1:H112" headerRowCount="1">
+  <autoFilter ref="A1:H112"/>
   <tableColumns count="8">
     <tableColumn id="1" name="data"/>
     <tableColumn id="2" name="marca"/>
@@ -714,10 +714,10 @@
         <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>3000993</t>
+          <t>3000998</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>6633968</t>
+          <t>5522799</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -18650,40 +18650,40 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Exomega Control Emolient Shower Oil
 Óleo Banho Calmante Comichão da Pele Atópica
 1000 ml</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/exomega-control-emolient-shower-oil-8605683.html</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr"/>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>8605683</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -19906,7 +19906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19974,188 +19974,4474 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>Eludril
+Breath Colutório Uso Diário
+Colutório Combate Mau Hálito
+500 ml</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/breath-colutorio-uso-diario-7757309.html</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>7757309</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Eludril
+Care Colutório Antiplaca
+Colutório Higiene Oral Reforçada
+500 ml</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/care-colutorio-antiplaca-4963445.html</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>4963445</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Cera Ortodôntica
+7 bandas</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/cera-ortodontica-6902380.html</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>6902380</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Eludril
+Classic Colutório
+Colutório Higiene Oral Específica
+200 ml</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/classic-colutorio-4910280.html</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>4910280</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Eludril
+Classic Colutório
+Colutório Higiene Oral Específica
+500 ml</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/classic-colutorio-4910281.html</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>4910281</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Arthrodont
+Colutório Gengival
+300 ml</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/colutorio-gengival-4131588.html</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>4131588</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Colutório Júnior Emoji
+500 ml</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/colutorio-junior-emoji-7607830.html</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>7607830</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Dentífrico Baby Bio
+30 ml</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/dentifrico-baby-bio-7697224.html</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>7697224</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Dentífrico Kids Timer
+50 ml</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/dentifrico-kids-timer-7616572.html</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>7616572</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Dentrífico Kids Morango Emoji
+50 ml</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/dentrifico-kids-morango-emoji-7607821.html</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>7607821</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Dentrifíco Sensileave Dentes Sensíveis
+50 ml</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/dentrifico-sensileave-dentes-sensiveis-7181157.html</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>7181157</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>IT Cosmetics
+Do It All Radiant Concealer
+Corretor de Olhos Iluminador Cobertura Média</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/do-it-all-radiant-concealer-450115.html</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>8375375</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
           <t>Elgydium
 Elgydium Fix Fixação Extra Forte
 45 g</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/elgydium-fix-fixacao-extra-forte-7434257.html</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>7434257</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Elgydium Fix Fixação Forte
 45 g</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/elgydium-fix-fixacao-forte-7434256.html</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>7434256</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Eludril
+EluPerio Colutório
+Colutório Saúde das Gengivas
+300 ml</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/eluperio-colutorio-4963443.html</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>4963443</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova Baby
+1 un</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-baby-7697227.html</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>7697227</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes 20 100 Soft
+1 un</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-20-100-soft-4031126.html</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>4031126</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Clinic 15 100 Suave
+1 un</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-clinic-15-100-suave-4032236.html</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>4032236</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Clinic 25 100 Média-Dura
+1 un</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-clinic-25-100-media-dura-4032977.html</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>4032977</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Clinic Pós-Cirúrgica 7 100
+1 un</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-clinic-pos-cirurgica-7-100-4033361.html</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>4033361</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Clinic Sensitive
+1 un</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-clinic-sensitive-6259715.html</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>6259715</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Diffusion Média
+1 un</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-diffusion-media-5105696.html</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>5105696</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Diffusion Suave
+1 un</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-diffusion-suave-5105695.html</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>5105695</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Interactive Dura
+1 un</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-interactive-dura-3065982.html</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>3065982</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Interactive Média
+1 un</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-interactive-media-3065979.html</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>3065979</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Interactive Suave
+1 un</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-interactive-suave-3065975.html</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>3065975</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Júnior 7-12 Anos
+1 un</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-junior-7-12-anos-3065981.html</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>3065981</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Junior Emoji
+1 un</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-junior-emoji-7607816.html</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>7607816</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Kids 2-6 Anos
+1 un</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-kids-2-6-anos-3851492.html</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>3851492</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Kids Emoji
+1 un</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-kids-emoji-7607814.html</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>7607814</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Kids Shark 2-6 Anos
+1 un</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-kids-shark-2-6-anos-5872405.html</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>5872405</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Medium 4 in 1
+Escova de Dentes Média
+1 un</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-medium-4-in-1-8437467.html</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>8437467</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Ortho X Adulto
+1 un</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-ortho-x-adulto-3690745.html</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>3690745</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Ortodôntica 7-12 Anos
+1 un</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-ortodontica-7-12-anos-4031802.html</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>4031802</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Periodôntica Ultra Suave
+1 un</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-periodontica-ultra-suave-4034487.html</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>4034487</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Pocket Suave
+1 un</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-pocket-suave-6259714.html</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>6259714</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Sensitive Souple Soft
+1 un</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-sensitive-souple-soft-3690744.html</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>3690744</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Soft 4 in 1
+Escova de Dentes Suave
+1 un</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-soft-4-in-1-8436212.html</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>8436212</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Whitening Média
+1 un</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-whitening-media-3690743.html</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>3690743</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova de Dentes Whitening Suave
+1 un</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-de-dentes-whitening-suave-3000659.html</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>3000659</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova Dentes Eco Média
+1 un</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-dentes-eco-media-7434320.html</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>7434320</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova Dentes Eco Suave
+1 un</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-dentes-eco-suave-7434319.html</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>7434319</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova Dentes Kids Eco
+1 un</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-dentes-kids-eco-7533801.html</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>7533801</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova Dentes Próteses Dentárias
+1 un</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-dentes-proteses-dentarias-4907334.html</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>4907334</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova Dentes Unicórnio 2-6 anos Kids Suave
+1 un</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-dentes-unicornio-2-6-anos-kids-suave-7925701.html</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>7925701</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova Style Reciclada Média
+1 un</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-style-reciclada-media-7697229.html</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>7697229</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escova Style Reciclada Suave
+1 un</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escova-style-reciclada-suave-7697232.html</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>7697232</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escovilhão Clinic Mono Compact Amarelo
+4 un</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escovilhao-clinic-mono-compact-amarelo-5815520.html</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>5815520</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escovilhão Clinic Mono Compact Azul
+4 un</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escovilhao-clinic-mono-compact-azul-5815519.html</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>5815519</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escovilhão Clinic Mono Compact Laranja
+4 un</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escovilhao-clinic-mono-compact-laranja-5815524.html</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>5815524</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escovilhão Clinic Mono Compact Roxo
+4 un</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escovilhao-clinic-mono-compact-roxo-5815549.html</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>5815549</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escovilhão Clinic Mono Compact Verde
+4 un</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escovilhao-clinic-mono-compact-verde-5815553.html</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>5815553</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escovilhão Clinic Mono Compact Vermelho
+4 un</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escovilhao-clinic-mono-compact-vermelho-5815530.html</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>5815530</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escovilhão Interdentário Laranja
+Recarga Escovilhão
+1 un</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escovilhao-interdentario-laranja-8420655.html</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>8420655</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escovilhão Recarga ISO1
+Escovilhão Interdentário Azul
+1 un</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escovilhao-recarga-iso1-8478522.html</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>8478522</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escovilhão Recarga ISO4
+Escovilhão Interdentário Vermelho
+1 un</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escovilhao-recarga-iso4-8478523.html</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>8478523</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escovilhões Clinic Mono Pretos
+4 un</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escovilhoes-clinic-mono-pretos-6937302.html</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>6937302</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Escovilhões Dental Picks
+36 un</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/escovilhoes-dental-picks-6451857.html</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>6451857</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Eludril
+Extra Colutório
+Colutório Higiene Oral Específica
+300 ml</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/extra-colutorio-6937438.html</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>6937438</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Fio Dentário Black
+1 un</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/fio-dentario-black-5786948.html</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>5786948</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Fio Dentário com Clorohexidina
+1 un</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/fio-dentario-com-clorohexidina-5036328.html</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>5036328</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Fio Dentário com Flúor
+1 un</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/fio-dentario-com-fluor-3066412.html</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr"/>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>3066412</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Fio Dentário Crossing Floss
+1 un</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/fio-dentario-crossing-floss-8099110.html</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>8099110</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Fio Dentário Expanding
+1 un</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/fio-dentario-expanding-3066410.html</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr"/>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>3066410</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Gel Cicallium
+8 ml</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/gel-cicallium-6637662.html</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>6637662</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Gel Dentário Sensibilidade Dentária
+30ml</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/gel-dentario-sensibilidade-dentaria-6637710.html</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr"/>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>6637710</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Gel Dentes Sensíveis
+75 ml</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/gel-dentes-sensiveis-3000688.html</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>3000688</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Gel Dentífrico Brilho e Cuidado
+30 ml</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/gel-dentifrico-brilho-e-cuidado-4708555.html</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr"/>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>4708555</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Elgydium
+Gel Dentífrico Júnior Pastilha Elástica
+50 ml</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>https://wells.pt/gel-dentifrico-junior-pastilha-elastica-4219095.html</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr"/>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>4219095</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Gel Dentífrico Kids Banana 2-6 Anos
+50 ml</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/gel-dentifrico-kids-banana-2-6-anos-5654019.html</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr"/>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>5654019</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Gel Dentífrico Kids Frutos Silvestres
+50 ml</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/gel-dentifrico-kids-frutos-silvestres-3000700.html</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>3000700</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Gel Dentífrico Menta Suave 7-12 Anos
+50 ml</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/gel-dentifrico-menta-suave-7-12-anos-6865620.html</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr"/>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>6865620</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>Parodium
 Gel Gengival
 50 ml</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-gengival-3065953.html</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>3065953</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>Sem desconto</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>Elugel
 Gel Redutor Placa Bacteriana
 40 ml</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-redutor-placa-bacteriana-3017892.html</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr"/>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>3017892</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>Sem desconto</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Eludril
+Gums Colutório Uso Diário
+Colutório Gengivas Sensíveis
+500 ml</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/gums-colutorio-uso-diario-7407474.html</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>7407474</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Lancôme
+Idole Peach'N Roses Eau de Parfum
+Perfume para Mulher Floral e Frutado
+25 ml</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/idole-peachn-roses-eau-de-parfum-446721.html</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>25 ml</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>8697790</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Lancôme
+Idole Peach'N Roses Eau de Parfum
+Perfume para Mulher Floral e Frutado
+25 ml</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/idole-peachn-roses-eau-de-parfum-446721.html</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>50 ml</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>8697791</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Lancôme
+Idole Peach'N Roses Eau de Parfum
+Perfume para Mulher Floral e Frutado
+25 ml</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/idole-peachn-roses-eau-de-parfum-446721.html</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>100 ml</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>8697789</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Eludril
+Intense Colutório Uso Diário
+Colutório Frescura Intensa
+500 ml</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/intense-colutorio-uso-diario-7181937.html</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>7181937</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Nyx Professional Makeup
+Jelly Job Full Bodied Shine Gloss
+Gloss Lábios Brilho Hidratante</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/jelly-job-full-bodied-shine-gloss-450316.html</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>8692113</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Sem desconto</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Elgydium
+Kit Viagem Higiene Oral
+1 un</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>https://wells.pt/kit-viagem-higiene-oral-5106725.html</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr"/>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>5106725</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Eludril
+Ortho Colutório Uso Diário
+Colutório Aparelhos Ortodônticos
+500 ml</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/ortho-colutorio-uso-diario-7631910.html</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr"/>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>7631910</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Pack Basic Trio Toothbrush Medium
+Escovas de Dentes Médias
+3 un</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/pack-basic-trio-toothbrush-medium-8547307.html</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>8547307</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Pack Junior Prevenção de Cáries
+Pack Escova e Pasta Dentífrica
+1 un</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/pack-junior-prevencao-de-caries-8547309.html</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr"/>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>8547309</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Pansoral Repair Gel Reparador
+15ml</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/pansoral-repair-gel-reparador-5036327.html</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>5036327</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Pasta de Dentes Branqueadora
+75 ml</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/pasta-de-dentes-branqueadora-3000690.html</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr"/>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>3000690</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Pasta de Dentes Branqueadora Cool Lemon
+75 ml</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/pasta-de-dentes-branqueadora-cool-lemon-5786938.html</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>5786938</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Arthrodont
+Pasta de Dentes Gengivas Irritadas
+75 ml</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/pasta-de-dentes-gengivas-irritadas-3045806.html</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr"/>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>3045806</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Pasta de Dentes Proteção Gengivas
+75 ml</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/pasta-de-dentes-protecao-gengivas-3000692.html</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>3000692</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
         <is>
           <t>Arthrodont
 Pasta Dentes Arthrodont Expert
 50 ml</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/pasta-dentes-arthrodont-expert-7323268.html</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="E91" s="5" t="inlineStr"/>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
         <is>
           <t>7323268</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Pasta Dentes Placa Bacteriana e Gengivas
+75 ml</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/pasta-dentes-placa-bacteriana-e-gengivas-7323267.html</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>7323267</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Arthrodont
+Pasta Dentífrica Gengivas Irritadas
+75 ml</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/pasta-dentifrica-gengivas-irritadas-7977172.html</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr"/>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>7977172</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Pasta Dentrífica Júnior Tutti Fruti Emoji
+50 ml</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/pasta-dentrifica-junior-tutti-fruti-emoji-7607823.html</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>7607823</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Premières Dents Gel de Massage
+Gel de Massagem Gengival para Bebé
+15 ml</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/premieres-dents-gel-de-massage-8608196.html</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr"/>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>8608196</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>Sem desconto</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Eludril
+Protect Colutório Uso Diário
+Colutório Proteção Dentes e Gengivas
+500 ml</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/protect-colutorio-uso-diario-7181924.html</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>7181924</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>Arthrodont
+Protect Gel Dentífrico Ácido Glicirretínico
+Gel Dentífrico Protetor Dentes e Gengivas
+75 ml</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>https://wells.pt/protect-gel-dentifrico-acido-glicirretinico-5047855.html</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr"/>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>5047855</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Arthrodont
+Protect + Gel Dentífrico Diário Com Fluor
+Gel Protetor Dentífrico Fortalecedor Gengivas
+75 ml</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/protect-gel-dentifrico-diario-com-fluor-8720519.html</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>8720519</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Raspador de Língua Breath
+1 un</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/raspador-de-lingua-breath-8071465.html</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr"/>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>8071465</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Refill Interdental Brushes ISO5
+Escovilhão Interdentário Roxo
+3 un</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/refill-interdental-brushes-iso5-8547079.html</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>8547079</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Refills Interdental Brushes Fine
+Escovilhão Interdentário Amarelo
+4 un</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/refills-interdental-brushes-fine-8414341.html</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr"/>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>8414341</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Refills Interdental Brushes Fine
+Escovilhão Interdentário Preto
+4 un</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/refills-interdental-brushes-fine-8414342.html</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>8414342</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Eludril
+Sensitive Colutório Uso Diário
+Colutório Proteção Dentes Sensíveis
+500 ml</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/sensitive-colutorio-uso-diario-7407495.html</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr"/>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>7407495</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Souple Soft Dragon 2-6A
+Escova de Dentes Criança Dragão
+1 un</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/souple-soft-dragon-2-6a-8513945.html</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>8513945</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Spray Cicallium
+15 ml</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/spray-cicallium-6637665.html</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr"/>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>6637665</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Spray Xeroleave Boca Seca
+70 ml</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/spray-xeroleave-boca-seca-6259717.html</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>6259717</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Tooth Decay Protection Intense Freshness
+Pasta de Dentes Prevenção Cáries com Fluorinol
+75 ml</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/tooth-decay-protection-intense-freshness-3000694.html</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr"/>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>3000694</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Toothpaste Gel Whitening 5 in 1
+Pasta Dentífrica Branqueamento
+75ml</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/toothpaste-gel-whitening-5-in-1-6830819.html</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr"/>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>6830819</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Trio Compact Interdental Brushes Fine
+Escovilhão Interdentário Muito Estreito Misto
+1 un</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/trio-compact-interdental-brushes-fine-8414367.html</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr"/>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>8414367</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Elgydium
+Trio Compact Interdental Brushes Fine Large
+Escovilhão Interdentário Largo Misto
+1 un</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/trio-compact-interdental-brushes-fine-large-8414338.html</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>8414338</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Elgydium
+Triocompact Escovilhão Estreito Misto
+Escovilhão Estreito Misto
+1 un</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/triocompact-escovilhao-estreito-misto-8420699.html</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr"/>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>8420699</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Eludril
+White Colutório Uso Diário
+Colutório Proteção Anti-Manchas
+500 ml</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/white-colutorio-uso-diario-7181934.html</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>7181934</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -20691,7 +24977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -21369,7 +25655,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>3000993</t>
+          <t>3000998</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -23134,342 +27420,462 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Lancôme
+Idole Peach'N Roses Eau de Parfum
+Perfume para Mulher Floral e Frutado
+25 ml</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>100 ml</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>8697789</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/idole-peachn-roses-eau-de-parfum-446721.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Lancôme
+Idole Peach'N Roses Eau de Parfum
+Perfume para Mulher Floral e Frutado
+25 ml</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>25 ml</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>8697790</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/idole-peachn-roses-eau-de-parfum-446721.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Lancôme
+Idole Peach'N Roses Eau de Parfum
+Perfume para Mulher Floral e Frutado
+25 ml</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>50 ml</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>8697791</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/idole-peachn-roses-eau-de-parfum-446721.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Forticea Strengthening Revitalizing Shampoo
 Champô Fortificante Todos Tipos de Cabelo</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>250ml</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>6759973</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/forticea-strengthening-revitalizing-shampoo-343991.html</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>Forticea Strengthening Revitalizing Shampoo
 Champô Fortificante Todos Tipos de Cabelo</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>7630905</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/forticea-strengthening-revitalizing-shampoo-343991.html</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Naturia Gentle Micellair Shampoo
 Champô Suave Uso Frequente e Familiar</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>6633968</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>5522799</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>Naturia Gentle Micellair Shampoo
 Champô Suave Uso Frequente e Familiar</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>400 ml</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
         <is>
           <t>7610972</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F71" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>Naturia Gentle Micellair Shampoo
 Champô Suave Uso Frequente e Familiar</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>5522799</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>Triphasic Active Grow Shampoo
 Champô Crescimento do Cabelo</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>8557861</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/triphasic-active-grow-shampoo-427541.html</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>Triphasic Active Grow Shampoo
 Champô Crescimento do Cabelo</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>500 ml</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>8557868</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/triphasic-active-grow-shampoo-427541.html</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Triphasic Active Grow Shampoo
 Champô Crescimento do Cabelo
 500 ml</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>8557861</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/triphasic-active-grow-shampoo-8557868.html</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>Triphasic Active Grow Shampoo
 Champô Crescimento do Cabelo
 500 ml</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>500 ml</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>8557868</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/triphasic-active-grow-shampoo-8557868.html</t>
         </is>

--- a/logs/Consolidado_05_03_2026.xlsx
+++ b/logs/Consolidado_05_03_2026.xlsx
@@ -269,8 +269,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Marca_Oral_Care" displayName="Marca_Oral_Care" ref="A1:H112" headerRowCount="1">
-  <autoFilter ref="A1:H112"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Marca_Oral_Care" displayName="Marca_Oral_Care" ref="A1:H107" headerRowCount="1">
+  <autoFilter ref="A1:H107"/>
   <tableColumns count="8">
     <tableColumn id="1" name="data"/>
     <tableColumn id="2" name="marca"/>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
         <v>3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>3000998</t>
+          <t>3000993</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>5522799</t>
+          <t>6633968</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -19906,7 +19906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20418,125 +20418,85 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>IT Cosmetics
-Do It All Radiant Concealer
-Corretor de Olhos Iluminador Cobertura Média</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/do-it-all-radiant-concealer-450115.html</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>8375375</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Oral Care</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
           <t>Elgydium
 Elgydium Fix Fixação Extra Forte
 45 g</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/elgydium-fix-fixacao-extra-forte-7434257.html</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>7434257</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Elgydium Fix Fixação Forte
 45 g</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/elgydium-fix-fixacao-forte-7434256.html</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>7434256</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Eludril
 EluPerio Colutório
@@ -20544,680 +20504,680 @@
 300 ml</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/eluperio-colutorio-4963443.html</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>4963443</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova Baby
 1 un</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-baby-7697227.html</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>7697227</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes 20 100 Soft
 1 un</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-20-100-soft-4031126.html</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>4031126</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Clinic 15 100 Suave
 1 un</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-clinic-15-100-suave-4032236.html</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>4032236</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Clinic 25 100 Média-Dura
 1 un</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-clinic-25-100-media-dura-4032977.html</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>4032977</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Clinic Pós-Cirúrgica 7 100
 1 un</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-clinic-pos-cirurgica-7-100-4033361.html</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>4033361</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Clinic Sensitive
 1 un</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-clinic-sensitive-6259715.html</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>6259715</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Diffusion Média
 1 un</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-diffusion-media-5105696.html</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>5105696</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Diffusion Suave
 1 un</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-diffusion-suave-5105695.html</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>5105695</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Interactive Dura
 1 un</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-interactive-dura-3065982.html</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>3065982</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Interactive Média
 1 un</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-interactive-media-3065979.html</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>3065979</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Interactive Suave
 1 un</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-interactive-suave-3065975.html</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>3065975</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Júnior 7-12 Anos
 1 un</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-junior-7-12-anos-3065981.html</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>3065981</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Junior Emoji
 1 un</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-junior-emoji-7607816.html</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>7607816</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Kids 2-6 Anos
 1 un</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-kids-2-6-anos-3851492.html</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>3851492</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Kids Emoji
 1 un</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-kids-emoji-7607814.html</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>7607814</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Kids Shark 2-6 Anos
 1 un</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-kids-shark-2-6-anos-5872405.html</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>5872405</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Medium 4 in 1
@@ -21225,240 +21185,240 @@
 1 un</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-medium-4-in-1-8437467.html</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>8437467</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Ortho X Adulto
 1 un</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-ortho-x-adulto-3690745.html</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>3690745</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Ortodôntica 7-12 Anos
 1 un</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-ortodontica-7-12-anos-4031802.html</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>4031802</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Periodôntica Ultra Suave
 1 un</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-periodontica-ultra-suave-4034487.html</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>4034487</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Pocket Suave
 1 un</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-pocket-suave-6259714.html</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>6259714</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Sensitive Souple Soft
 1 un</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-sensitive-souple-soft-3690744.html</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>3690744</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Soft 4 in 1
@@ -21466,640 +21426,640 @@
 1 un</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-soft-4-in-1-8436212.html</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>8436212</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Whitening Média
 1 un</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-whitening-media-3690743.html</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>3690743</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Whitening Suave
 1 un</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-whitening-suave-3000659.html</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>3000659</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova Dentes Eco Média
 1 un</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-dentes-eco-media-7434320.html</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>7434320</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova Dentes Eco Suave
 1 un</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-dentes-eco-suave-7434319.html</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr"/>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>7434319</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova Dentes Kids Eco
 1 un</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-dentes-kids-eco-7533801.html</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>7533801</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova Dentes Próteses Dentárias
 1 un</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-dentes-proteses-dentarias-4907334.html</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>4907334</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova Dentes Unicórnio 2-6 anos Kids Suave
 1 un</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-dentes-unicornio-2-6-anos-kids-suave-7925701.html</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>7925701</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escova Style Reciclada Média
 1 un</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-style-reciclada-media-7697229.html</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>7697229</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escova Style Reciclada Suave
 1 un</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-style-reciclada-suave-7697232.html</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>7697232</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhão Clinic Mono Compact Amarelo
 4 un</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhao-clinic-mono-compact-amarelo-5815520.html</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>5815520</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhão Clinic Mono Compact Azul
 4 un</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhao-clinic-mono-compact-azul-5815519.html</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>5815519</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhão Clinic Mono Compact Laranja
 4 un</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhao-clinic-mono-compact-laranja-5815524.html</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>5815524</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhão Clinic Mono Compact Roxo
 4 un</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhao-clinic-mono-compact-roxo-5815549.html</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>5815549</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhão Clinic Mono Compact Verde
 4 un</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhao-clinic-mono-compact-verde-5815553.html</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr"/>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>5815553</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhão Clinic Mono Compact Vermelho
 4 un</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhao-clinic-mono-compact-vermelho-5815530.html</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>5815530</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhão Interdentário Laranja
@@ -22107,40 +22067,40 @@
 1 un</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhao-interdentario-laranja-8420655.html</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>8420655</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhão Recarga ISO1
@@ -22148,40 +22108,40 @@
 1 un</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhao-recarga-iso1-8478522.html</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>8478522</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhão Recarga ISO4
@@ -22189,120 +22149,120 @@
 1 un</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhao-recarga-iso4-8478523.html</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>8478523</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhões Clinic Mono Pretos
 4 un</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhoes-clinic-mono-pretos-6937302.html</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>6937302</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhões Dental Picks
 36 un</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhoes-dental-picks-6451857.html</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>6451857</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Eludril
 Extra Colutório
@@ -22310,640 +22270,640 @@
 300 ml</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/extra-colutorio-6937438.html</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>6937438</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Fio Dentário Black
 1 un</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/fio-dentario-black-5786948.html</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr"/>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>5786948</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Fio Dentário com Clorohexidina
 1 un</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/fio-dentario-com-clorohexidina-5036328.html</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>5036328</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Fio Dentário com Flúor
 1 un</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/fio-dentario-com-fluor-3066412.html</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr"/>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>3066412</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Fio Dentário Crossing Floss
 1 un</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/fio-dentario-crossing-floss-8099110.html</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr"/>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>8099110</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Fio Dentário Expanding
 1 un</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/fio-dentario-expanding-3066410.html</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr"/>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>3066410</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Gel Cicallium
 8 ml</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-cicallium-6637662.html</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr"/>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>6637662</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Gel Dentário Sensibilidade Dentária
 30ml</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-dentario-sensibilidade-dentaria-6637710.html</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr"/>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>6637710</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Gel Dentes Sensíveis
 75 ml</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-dentes-sensiveis-3000688.html</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr"/>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>3000688</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Gel Dentífrico Brilho e Cuidado
 30 ml</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-dentifrico-brilho-e-cuidado-4708555.html</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr"/>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>4708555</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Gel Dentífrico Júnior Pastilha Elástica
 50 ml</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-dentifrico-junior-pastilha-elastica-4219095.html</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr"/>
-      <c r="F70" s="8" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr"/>
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G70" s="7" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>4219095</t>
         </is>
       </c>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Gel Dentífrico Kids Banana 2-6 Anos
 50 ml</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-dentifrico-kids-banana-2-6-anos-5654019.html</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr"/>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>5654019</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Gel Dentífrico Kids Frutos Silvestres
 50 ml</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-dentifrico-kids-frutos-silvestres-3000700.html</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr"/>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr"/>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>3000700</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Gel Dentífrico Menta Suave 7-12 Anos
 50 ml</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-dentifrico-menta-suave-7-12-anos-6865620.html</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr"/>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>6865620</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>Parodium
 Gel Gengival
 50 ml</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-gengival-3065953.html</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr"/>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>3065953</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>Sem desconto</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>Elugel
 Gel Redutor Placa Bacteriana
 40 ml</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-redutor-placa-bacteriana-3017892.html</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr"/>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>3017892</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>Sem desconto</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>Eludril
 Gums Colutório Uso Diário
@@ -22951,175 +22911,40 @@
 500 ml</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/gums-colutorio-uso-diario-7407474.html</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr"/>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr"/>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>7407474</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>Lancôme
-Idole Peach'N Roses Eau de Parfum
-Perfume para Mulher Floral e Frutado
-25 ml</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/idole-peachn-roses-eau-de-parfum-446721.html</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>25 ml</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>8697790</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>Oral Care</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>Lancôme
-Idole Peach'N Roses Eau de Parfum
-Perfume para Mulher Floral e Frutado
-25 ml</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/idole-peachn-roses-eau-de-parfum-446721.html</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>50 ml</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>8697791</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>Oral Care</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>Lancôme
-Idole Peach'N Roses Eau de Parfum
-Perfume para Mulher Floral e Frutado
-25 ml</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/idole-peachn-roses-eau-de-parfum-446721.html</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>100 ml</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>8697789</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>Oral Care</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>Eludril
 Intense Colutório Uso Diário
@@ -23127,120 +22952,80 @@
 500 ml</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/intense-colutorio-uso-diario-7181937.html</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>7181937</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>Nyx Professional Makeup
-Jelly Job Full Bodied Shine Gloss
-Gloss Lábios Brilho Hidratante</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/jelly-job-full-bodied-shine-gloss-450316.html</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr"/>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>8692113</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>Sem desconto</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Oral Care</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Kit Viagem Higiene Oral
 1 un</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/kit-viagem-higiene-oral-5106725.html</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr"/>
-      <c r="F82" s="8" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr"/>
+      <c r="F77" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G82" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>5106725</t>
         </is>
       </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>Eludril
 Ortho Colutório Uso Diário
@@ -23248,40 +23033,40 @@
 500 ml</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/ortho-colutorio-uso-diario-7631910.html</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr"/>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>7631910</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Pack Basic Trio Toothbrush Medium
@@ -23289,40 +23074,40 @@
 3 un</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/pack-basic-trio-toothbrush-medium-8547307.html</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr"/>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>8547307</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Pack Junior Prevenção de Cáries
@@ -23330,400 +23115,400 @@
 1 un</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/pack-junior-prevencao-de-caries-8547309.html</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr"/>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>8547309</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Pansoral Repair Gel Reparador
 15ml</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/pansoral-repair-gel-reparador-5036327.html</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr"/>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>5036327</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Pasta de Dentes Branqueadora
 75 ml</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/pasta-de-dentes-branqueadora-3000690.html</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr"/>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
         <is>
           <t>3000690</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Pasta de Dentes Branqueadora Cool Lemon
 75 ml</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/pasta-de-dentes-branqueadora-cool-lemon-5786938.html</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr"/>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr"/>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>5786938</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>Arthrodont
 Pasta de Dentes Gengivas Irritadas
 75 ml</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/pasta-de-dentes-gengivas-irritadas-3045806.html</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr"/>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <t>3045806</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Pasta de Dentes Proteção Gengivas
 75 ml</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/pasta-de-dentes-protecao-gengivas-3000692.html</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="E85" s="5" t="inlineStr"/>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>3000692</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>Arthrodont
 Pasta Dentes Arthrodont Expert
 50 ml</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/pasta-dentes-arthrodont-expert-7323268.html</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr"/>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
         <is>
           <t>7323268</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Pasta Dentes Placa Bacteriana e Gengivas
 75 ml</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/pasta-dentes-placa-bacteriana-e-gengivas-7323267.html</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr"/>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>7323267</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>Arthrodont
 Pasta Dentífrica Gengivas Irritadas
 75 ml</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/pasta-dentifrica-gengivas-irritadas-7977172.html</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr"/>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
         <is>
           <t>7977172</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Pasta Dentrífica Júnior Tutti Fruti Emoji
 50 ml</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/pasta-dentrifica-junior-tutti-fruti-emoji-7607823.html</t>
         </is>
       </c>
-      <c r="E94" s="3" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr"/>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>7607823</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Premières Dents Gel de Massage
@@ -23731,40 +23516,40 @@
 15 ml</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/premieres-dents-gel-de-massage-8608196.html</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr"/>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>8608196</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>Sem desconto</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
         <is>
           <t>Eludril
 Protect Colutório Uso Diário
@@ -23772,40 +23557,40 @@
 500 ml</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/protect-colutorio-uso-diario-7181924.html</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr">
+      <c r="E91" s="5" t="inlineStr"/>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
         <is>
           <t>7181924</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>Arthrodont
 Protect Gel Dentífrico Ácido Glicirretínico
@@ -23813,40 +23598,40 @@
 75 ml</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/protect-gel-dentifrico-acido-glicirretinico-5047855.html</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr"/>
-      <c r="F97" s="8" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
         <is>
           <t>5047855</t>
         </is>
       </c>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>Arthrodont
 Protect + Gel Dentífrico Diário Com Fluor
@@ -23854,80 +23639,80 @@
 75 ml</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/protect-gel-dentifrico-diario-com-fluor-8720519.html</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr"/>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>8720519</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Raspador de Língua Breath
 1 un</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/raspador-de-lingua-breath-8071465.html</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr"/>
-      <c r="F99" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
         <is>
           <t>8071465</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Refill Interdental Brushes ISO5
@@ -23935,40 +23720,40 @@
 3 un</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/refill-interdental-brushes-iso5-8547079.html</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
+      <c r="E95" s="5" t="inlineStr"/>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>8547079</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Refills Interdental Brushes Fine
@@ -23976,40 +23761,40 @@
 4 un</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/refills-interdental-brushes-fine-8414341.html</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr"/>
-      <c r="F101" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
         <is>
           <t>8414341</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Refills Interdental Brushes Fine
@@ -24017,40 +23802,40 @@
 4 un</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/refills-interdental-brushes-fine-8414342.html</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
+      <c r="E97" s="5" t="inlineStr"/>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <t>8414342</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>Eludril
 Sensitive Colutório Uso Diário
@@ -24058,40 +23843,40 @@
 500 ml</t>
         </is>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/sensitive-colutorio-uso-diario-7407495.html</t>
         </is>
       </c>
-      <c r="E103" s="5" t="inlineStr"/>
-      <c r="F103" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
         <is>
           <t>7407495</t>
         </is>
       </c>
-      <c r="H103" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Souple Soft Dragon 2-6A
@@ -24099,120 +23884,120 @@
 1 un</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/souple-soft-dragon-2-6a-8513945.html</t>
         </is>
       </c>
-      <c r="E104" s="3" t="inlineStr"/>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr">
+      <c r="E99" s="5" t="inlineStr"/>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>8513945</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Spray Cicallium
 15 ml</t>
         </is>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/spray-cicallium-6637665.html</t>
         </is>
       </c>
-      <c r="E105" s="5" t="inlineStr"/>
-      <c r="F105" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <t>6637665</t>
         </is>
       </c>
-      <c r="H105" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Spray Xeroleave Boca Seca
 70 ml</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/spray-xeroleave-boca-seca-6259717.html</t>
         </is>
       </c>
-      <c r="E106" s="3" t="inlineStr"/>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr"/>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <t>6259717</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Tooth Decay Protection Intense Freshness
@@ -24220,40 +24005,40 @@
 75 ml</t>
         </is>
       </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/tooth-decay-protection-intense-freshness-3000694.html</t>
         </is>
       </c>
-      <c r="E107" s="5" t="inlineStr"/>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
         <is>
           <t>3000694</t>
         </is>
       </c>
-      <c r="H107" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Toothpaste Gel Whitening 5 in 1
@@ -24261,40 +24046,40 @@
 75ml</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/toothpaste-gel-whitening-5-in-1-6830819.html</t>
         </is>
       </c>
-      <c r="E108" s="3" t="inlineStr"/>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr">
+      <c r="E103" s="5" t="inlineStr"/>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
         <is>
           <t>6830819</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Trio Compact Interdental Brushes Fine
@@ -24302,40 +24087,40 @@
 1 un</t>
         </is>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/trio-compact-interdental-brushes-fine-8414367.html</t>
         </is>
       </c>
-      <c r="E109" s="5" t="inlineStr"/>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
         <is>
           <t>8414367</t>
         </is>
       </c>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
         <is>
           <t>Elgydium
 Trio Compact Interdental Brushes Fine Large
@@ -24343,40 +24128,40 @@
 1 un</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/trio-compact-interdental-brushes-fine-large-8414338.html</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr">
+      <c r="E105" s="5" t="inlineStr"/>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
         <is>
           <t>8414338</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>Elgydium
 Triocompact Escovilhão Estreito Misto
@@ -24384,40 +24169,40 @@
 1 un</t>
         </is>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/triocompact-escovilhao-estreito-misto-8420699.html</t>
         </is>
       </c>
-      <c r="E111" s="5" t="inlineStr"/>
-      <c r="F111" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
         <is>
           <t>8420699</t>
         </is>
       </c>
-      <c r="H111" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>Eludril
 White Colutório Uso Diário
@@ -24425,23 +24210,23 @@
 500 ml</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/white-colutorio-uso-diario-7181934.html</t>
         </is>
       </c>
-      <c r="E112" s="3" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="inlineStr">
+      <c r="E107" s="5" t="inlineStr"/>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
         <is>
           <t>7181934</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
+      <c r="H107" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -24977,7 +24762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -25655,7 +25440,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>3000998</t>
+          <t>3000993</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -27420,20 +27205,18 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>René Furterer</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Lancôme
-Idole Peach'N Roses Eau de Parfum
-Perfume para Mulher Floral e Frutado
-25 ml</t>
+          <t>Forticea Strengthening Revitalizing Shampoo
+Champô Fortificante Todos Tipos de Cabelo</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>100 ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -27443,7 +27226,7 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>8697789</t>
+          <t>6759973</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -27453,27 +27236,25 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://wells.pt/idole-peachn-roses-eau-de-parfum-446721.html</t>
+          <t>https://wells.pt/forticea-strengthening-revitalizing-shampoo-343991.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>René Furterer</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Lancôme
-Idole Peach'N Roses Eau de Parfum
-Perfume para Mulher Floral e Frutado
-25 ml</t>
+          <t>Forticea Strengthening Revitalizing Shampoo
+Champô Fortificante Todos Tipos de Cabelo</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>25 ml</t>
+          <t>50 ml</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -27483,57 +27264,55 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>8697790</t>
+          <t>7630905</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://wells.pt/idole-peachn-roses-eau-de-parfum-446721.html</t>
+          <t>https://wells.pt/forticea-strengthening-revitalizing-shampoo-343991.html</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>Oral Care</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>Lancôme
-Idole Peach'N Roses Eau de Parfum
-Perfume para Mulher Floral e Frutado
-25 ml</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>50 ml</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>8697791</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/idole-peachn-roses-eau-de-parfum-446721.html</t>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>René Furterer</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Naturia Gentle Micellair Shampoo
+Champô Suave Uso Frequente e Familiar</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>200 ml</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>6633968</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
         </is>
       </c>
     </row>
@@ -27545,13 +27324,13 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Forticea Strengthening Revitalizing Shampoo
-Champô Fortificante Todos Tipos de Cabelo</t>
+          <t>Naturia Gentle Micellair Shampoo
+Champô Suave Uso Frequente e Familiar</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>250ml</t>
+          <t>400 ml</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -27561,7 +27340,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>6759973</t>
+          <t>7610972</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -27571,7 +27350,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://wells.pt/forticea-strengthening-revitalizing-shampoo-343991.html</t>
+          <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
         </is>
       </c>
     </row>
@@ -27583,8 +27362,8 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Forticea Strengthening Revitalizing Shampoo
-Champô Fortificante Todos Tipos de Cabelo</t>
+          <t>Naturia Gentle Micellair Shampoo
+Champô Suave Uso Frequente e Familiar</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -27599,7 +27378,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>7630905</t>
+          <t>5522799</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -27609,7 +27388,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>https://wells.pt/forticea-strengthening-revitalizing-shampoo-343991.html</t>
+          <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
         </is>
       </c>
     </row>
@@ -27621,8 +27400,8 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Naturia Gentle Micellair Shampoo
-Champô Suave Uso Frequente e Familiar</t>
+          <t>Triphasic Active Grow Shampoo
+Champô Crescimento do Cabelo</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -27637,17 +27416,17 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>5522799</t>
+          <t>8557861</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
+          <t>https://wells.pt/triphasic-active-grow-shampoo-427541.html</t>
         </is>
       </c>
     </row>
@@ -27659,223 +27438,109 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Naturia Gentle Micellair Shampoo
-Champô Suave Uso Frequente e Familiar</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>400 ml</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>7610972</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>René Furterer</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>Naturia Gentle Micellair Shampoo
-Champô Suave Uso Frequente e Familiar</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>50 ml</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>5522799</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>René Furterer</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
           <t>Triphasic Active Grow Shampoo
 Champô Crescimento do Cabelo</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>8557861</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>8557868</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/triphasic-active-grow-shampoo-427541.html</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>Triphasic Active Grow Shampoo
-Champô Crescimento do Cabelo</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>500 ml</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>8557868</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>https://wells.pt/triphasic-active-grow-shampoo-427541.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>René Furterer</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>Triphasic Active Grow Shampoo
 Champô Crescimento do Cabelo
 500 ml</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>8557861</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/triphasic-active-grow-shampoo-8557868.html</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>Triphasic Active Grow Shampoo
 Champô Crescimento do Cabelo
 500 ml</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>500 ml</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>8557868</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/triphasic-active-grow-shampoo-8557868.html</t>
         </is>
